--- a/dummy_data.xlsx
+++ b/dummy_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\sadoon97\playground\flux_v1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\sadoon97\playground\r20_validator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1EDF8D9-CDD3-4A24-93B5-D9857A75371E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A0BE942-4DE3-4626-97D1-E10750D8AACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3804" yWindow="3804" windowWidth="30960" windowHeight="12120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="732" yWindow="732" windowWidth="30960" windowHeight="12120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sales Sheet" sheetId="2" r:id="rId1"/>
@@ -182,6 +182,19 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A6ECD442-A0CD-4AD4-BCAE-5FE5FBBEE67E}" name="Table1" displayName="Table1" ref="B4:E8" totalsRowShown="0">
+  <autoFilter ref="B4:E8" xr:uid="{A6ECD442-A0CD-4AD4-BCAE-5FE5FBBEE67E}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{AC60ECA3-143A-4300-B5B6-4CE8C46FFD2E}" name="order_id"/>
+    <tableColumn id="2" xr3:uid="{485E3704-6CAE-4074-A5BC-75AB9DD8C2A6}" name="customer_id"/>
+    <tableColumn id="3" xr3:uid="{AB5202CF-B46C-4988-BCE0-28ED0E20E0CD}" name="customer_name"/>
+    <tableColumn id="4" xr3:uid="{72AC4032-2E5A-4104-878D-D06FA08C22F5}" name="customer_address"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -650,10 +663,10 @@
   <dimension ref="B4:E8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" customWidth="1"/>
+    <col min="4" max="4" width="16.5546875" customWidth="1"/>
+    <col min="5" max="5" width="18.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="4" spans="2:5" x14ac:dyDescent="0.3">
@@ -728,5 +741,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>